--- a/data/trans_bre/P45C_R1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,83</t>
+          <t>-0,77; 0,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,32</t>
+          <t>-0,62; 1,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,71</t>
+          <t>-1,18; 0,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,2</t>
+          <t>-2,86; 0,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,69; 136,42</t>
+          <t>-55,32; 160,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 193,03</t>
+          <t>-40,54; 220,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-74,54; 153,24</t>
+          <t>-75,45; 204,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-78,56; 16,41</t>
+          <t>-78,76; 7,34</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,95</t>
+          <t>-1,07; 0,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,94</t>
+          <t>-0,77; 0,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,0</t>
+          <t>-0,31; 1,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,83</t>
+          <t>-0,91; 0,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 62,82</t>
+          <t>-40,79; 64,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,72; 90,75</t>
+          <t>-42,11; 84,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 152,44</t>
+          <t>-27,11; 169,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 86,01</t>
+          <t>-46,94; 79,33</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,17</t>
+          <t>-1,41; 2,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,07</t>
+          <t>-0,41; 3,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,44</t>
+          <t>-1,19; 1,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,39</t>
+          <t>-1,65; 1,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,4; 258,91</t>
+          <t>-58,11; 234,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 605,56</t>
+          <t>-42,65; 646,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-84,22; 708,45</t>
+          <t>-89,88; 580,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 126,66</t>
+          <t>-59,23; 198,22</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,6</t>
+          <t>-0,67; 0,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,91</t>
+          <t>-0,31; 0,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,67</t>
+          <t>-0,36; 0,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,46</t>
+          <t>-0,93; 0,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 44,34</t>
+          <t>-33,1; 47,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 81,97</t>
+          <t>-21,77; 81,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 97,26</t>
+          <t>-32,85; 82,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 36,46</t>
+          <t>-44,56; 37,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P45C_R1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-1,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-49,97%</t>
+          <t>-50,02%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,83</t>
+          <t>-0,81; 0,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,3</t>
+          <t>-0,51; 1,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,74</t>
+          <t>-1,16; 0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,09</t>
+          <t>-2,71; 0,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,32; 160,13</t>
+          <t>-55,85; 184,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 220,04</t>
+          <t>-36,52; 230,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 204,25</t>
+          <t>-73,79; 188,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-78,76; 7,34</t>
+          <t>-77,55; 30,85</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,43%</t>
+          <t>-0,49%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,98</t>
+          <t>-1,07; 1,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,86</t>
+          <t>-0,72; 0,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,06</t>
+          <t>-0,3; 1,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,79</t>
+          <t>-0,85; 0,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 64,19</t>
+          <t>-41,05; 62,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 84,25</t>
+          <t>-38,74; 85,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 169,12</t>
+          <t>-27,88; 165,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 79,33</t>
+          <t>-42,19; 71,9</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,2</t>
+          <t>-1,29; 2,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,16</t>
+          <t>-0,41; 3,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,38</t>
+          <t>-1,29; 1,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,68</t>
+          <t>-1,6; 1,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 234,38</t>
+          <t>-58,72; 242,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 646,02</t>
+          <t>-34,78; 708,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-89,88; 580,61</t>
+          <t>-81,38; 772,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,23; 198,22</t>
+          <t>-57,2; 158,16</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,79%</t>
+          <t>-10,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,65</t>
+          <t>-0,63; 0,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,88</t>
+          <t>-0,29; 0,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,63</t>
+          <t>-0,32; 0,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,44</t>
+          <t>-0,81; 0,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 47,06</t>
+          <t>-31,66; 48,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 81,47</t>
+          <t>-18,47; 92,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 82,08</t>
+          <t>-28,87; 102,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 37,49</t>
+          <t>-37,74; 36,45</t>
         </is>
       </c>
     </row>
